--- a/docs/就職活動メモシステム.画面設計書.xlsx
+++ b/docs/就職活動メモシステム.画面設計書.xlsx
@@ -2074,7 +2074,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　全メモをIDの昇順で一覧表示する。表示する列は項目設定（item_settings）で「表示する」となっている項目のみとし、列の見出しには表示名を用いる。「No.」列にはIDではなく、先頭からの行番号を表示する。明細の先頭列には操作列（編集・削除ボタン）を置く。セルの文字は上寄せで表示する。各項目の値は、項目設定の表示桁数のバイト数（UTF-8）までを表示し、超える部分は表示しない（文字の泣き別れが起きないよう、文字を分割せず、バイト数が収まる文字までを表示する）。チェックボックス項目（項目設定で型が「チェックボックス」の項目）の値はチェックボックスで表示する（1でON、0でOFF。一覧では表示専用）。数値型（項目設定で型が「数値型」の項目）の値はカンマ区切りで、右寄せで表示する。登録日時・更新日時列の幅と表示書式は、共通のコードマスタ（code_masters、システムID=0）のコードID「registered_at」・「updated_at」の「表示桁数」と「初期値」（表示書式）に従う。検索部は初期状態では閉じている。</t>
+          <t xml:space="preserve">　　全メモをIDの昇順で一覧表示する。表示する列は項目設定（item_settings）で「表示する」となっている項目のみとし、列の見出しには表示名を用いる。「No.」列にはIDではなく、先頭からの行番号を表示する。明細の先頭列には操作列（編集・削除ボタン）を置く。セルの文字は上寄せで表示する。各項目の値は、項目設定の表示桁数のバイト数（UTF-8）までを表示し、超える部分は表示しない（文字の泣き別れが起きないよう、文字を分割せず、バイト数が収まる文字までを表示する）。チェックボックス項目（項目設定で型が「チェックボックス」の項目）の値はチェックボックスで表示する（1でON、0でOFF。一覧では表示専用）。数値型（項目設定で型が「数値型」の項目）の値はカンマ区切りで、右寄せで表示する。日付型（項目設定で型が「日付型」の項目）の値は、保存値（数字のみ yyyyMMdd）を yyyy/mm/dd 形式で表示する。登録日時・更新日時列の幅と表示書式は、共通のコードマスタ（code_masters、システムID=0）のコードID「registered_at」・「updated_at」の「表示桁数」と「初期値」（表示書式）に従う。検索部は初期状態では閉じている。</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3362,7 +3362,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　対象メモの現在の値を初期表示する（新規登録時は、項目設定の「初期値」に指定された値を初期表示する。初期値に含まれる %Y・%m・%d・%H・%i・%s はシステム日時へ置換する。複合指定も可： 例 %Y%m は当月の年月）。入力部品は項目設定に従い生成する（文字列型＝テキストボックス、メモ型＝テキストエリア、URL項目は幅広のテキストボックス）。コードIDが指定された項目は、コードマスタの文字列1を選択肢とするドロップダウンリストとし、選択した設定コードを保存値とする。チェックボックス項目（項目設定で型が「チェックボックス」の項目）はチェックボックスで入力し、チェック状態を1（ON）／0（OFF）として保存する。必須項目（項目設定で必須指定）には、項目名ラベルへ赤い「*」を表示する。登録日時・登録ユーザー・更新日時・更新ユーザー（監査項目）も表示する。削除ボタンは置かない（削除は一覧画面のみ）。</t>
+          <t xml:space="preserve">　　対象メモの現在の値を初期表示する（新規登録時は、項目設定の「初期値」に指定された値を初期表示する。初期値に含まれる %Y・%m・%d・%H・%i・%s はシステム日時へ置換する。複合指定も可： 例 %Y%m は当月の年月）。入力部品は項目設定に従い生成する（文字列型＝テキストボックス、メモ型＝テキストエリア、URL項目は幅広のテキストボックス）。コードIDが指定された項目は、コードマスタの文字列1を選択肢とするドロップダウンリストとし、選択した設定コードを保存値とする。チェックボックス項目（項目設定で型が「チェックボックス」の項目）はチェックボックスで入力し、チェック状態を1（ON）／0（OFF）として保存する。日付型項目（項目設定で型が「日付型」の項目）はカレンダーで入力し、yyyy/mm/dd で表示し、数字のみ（yyyyMMdd）で保存する。必須項目（項目設定で必須指定）には、項目名ラベルへ赤い「*」を表示する。登録日時・登録ユーザー・更新日時・更新ユーザー（監査項目）も表示する。削除ボタンは置かない（削除は一覧画面のみ）。</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　C. 一覧へ戻る： [9] 押下によりメモ一覧画面へ遷移する。</t>
+          <t xml:space="preserve">　　C. 一覧へ戻る： [10] 押下によりメモ一覧画面へ遷移する。</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3716,47 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>必須マーク</t>
+          <t>項目（日付型）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>型が「日付型」の項目</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>ラベル（赤い「*」）</t>
+          <t>カレンダー入力</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN/OUT</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>文字列</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>必須項目の項目名ラベルに表示</t>
+          <t>項目設定で型が「日付型」の項目。yyyy/mm/dd で表示し、数字のみ（yyyyMMdd）で保存。新規登録時は初期値で表示</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>項目設定で必須指定の項目のみ○</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>item_settings</t>
+          <t>memo_records</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>is_required</t>
+          <t>item_01～item_50</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>テキストボックスの幅</t>
+          <t>必須マーク</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ラベル（赤い「*」）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>文字列型の入力欄の幅は、共通のコードマスタ（システムID=0）のコードID「width_edit_textbox」の「幅」（文字列3）に従う</t>
+          <t>必須項目の項目名ラベルに表示</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>code_masters</t>
+          <t>item_settings</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>text_3</t>
+          <t>is_required</t>
         </is>
       </c>
     </row>
@@ -3816,17 +3816,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>登録日時・登録ユーザー／更新日時・更新ユーザー</t>
+          <t>テキストボックスの幅</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>registeredAt / registeredBy / updatedAt / updatedBy</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>ラベル</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>日時／文字列</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>常に表示（新規登録時は保存後に表示）。登録・更新ユーザーにはログイン中ユーザーIDが記録される</t>
+          <t>文字列型の入力欄の幅は、共通のコードマスタ（システムID=0）のコードID「width_edit_textbox」の「幅」（文字列3）に従う</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>memo_records</t>
+          <t>code_masters</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>registered_at / registered_by / updated_at / updated_by</t>
+          <t>text_3</t>
         </is>
       </c>
     </row>
@@ -3866,32 +3866,32 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>一覧に戻るボタン</t>
+          <t>登録日時・登録ユーザー／更新日時・更新ユーザー</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>registeredAt / registeredBy / updatedAt / updatedBy</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>ボタン</t>
+          <t>ラベル</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>日時／文字列</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>常に表示</t>
+          <t>常に表示（新規登録時は保存後に表示）。登録・更新ユーザーにはログイン中ユーザーIDが記録される</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>memo_records</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>registered_at / registered_by / updated_at / updated_by</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>キャンセルボタン</t>
+          <t>一覧に戻るボタン</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3966,137 +3966,187 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>キャンセルボタン</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>ボタン</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>常に表示</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>登録／変更を確定ボタン</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>ボタン</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>常に表示</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>バリデーション</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>バリデーション内容</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>エラーメッセージ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>必須項目（項目設定で必須指定）</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>保存時に未入力（ドロップダウンリストは未選択）でないこと</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>（項目名）は必須です</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>項目（コードID指定）</t>
+          <t>必須項目（項目設定で必須指定）</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>コードマスタに存在する設定コードであること</t>
+          <t>保存時に未入力（ドロップダウンリストは未選択）でないこと</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>（サーバ側検証エラー時）入力に問題があり、サーバーで処理できませんでした</t>
+          <t>（項目名）は必須です</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>項目（チェックボックス）</t>
+          <t>項目（コードID指定）</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>チェック状態を1（ON）／0（OFF）として保存すること</t>
+          <t>コードマスタに存在する設定コードであること</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>（サーバ側検証エラー時）入力に問題があり、サーバーで処理できませんでした</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>項目（チェックボックス）</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>チェック状態を1（ON）／0（OFF）として保存すること</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>―（サーバ側検証）</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>サーバ側バリデーション（Bean Validation）でエラーとなった場合</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>入力に問題があり、サーバーで処理できませんでした</t>
         </is>
@@ -4501,7 +4551,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>文字列型（STRING）／数値型（NUMERIC）／メモ型（MEMO）／チェックボックス（CHECKBOX）</t>
+          <t>文字列型（STRING）／数値型（NUMERIC）／メモ型（MEMO）／チェックボックス（CHECKBOX）／日付型（DATE）</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
